--- a/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
+++ b/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="MAP" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
   <si>
     <t>MAP: TaxReturn</t>
   </si>
@@ -671,6 +671,33 @@
   </si>
   <si>
     <t># Multiple instance entities</t>
+  </si>
+  <si>
+    <t>## CREATE ENTITIES (entity | tag | id)</t>
+  </si>
+  <si>
+    <t>credit</t>
+  </si>
+  <si>
+    <t>constants</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>## ENTITIES (name | number: 1 or *)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>## INITIALIZATION (entity | push)</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
@@ -1045,9 +1072,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="2" min="1" width="35"/>
     <col customWidth="true" max="3" min="3" width="20"/>
@@ -4010,6 +4038,444 @@
       <c r="C224" s="6"/>
       <c r="D224" s="6"/>
     </row>
+    <row r="225">
+      <c r="A225" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B225" s="6"/>
+      <c r="C225" s="6"/>
+      <c r="D225" s="6"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D226" s="2"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227" s="2"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D228" s="2"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D229" s="2"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230" s="2"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D231" s="2"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D232" s="2"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D233" s="2"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D234" s="2"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D235" s="2"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D236" s="2"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D237" s="2"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D238" s="2"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D239" s="2"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D240" s="2"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D241" s="2"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D242" s="2"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B243" s="6"/>
+      <c r="C243" s="6"/>
+      <c r="D243" s="6"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B262" s="6"/>
+      <c r="C262" s="6"/>
+      <c r="D262" s="6"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
+++ b/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
   <si>
     <t>MAP: TaxReturn</t>
   </si>
@@ -673,7 +673,28 @@
     <t># Multiple instance entities</t>
   </si>
   <si>
-    <t>## CREATE ENTITIES (entity | tag | id)</t>
+    <t>## CREATE ENTITIES (entity | tag | id | list)</t>
+  </si>
+  <si>
+    <t>taxpayers</t>
+  </si>
+  <si>
+    <t>dependents</t>
+  </si>
+  <si>
+    <t>incomes</t>
+  </si>
+  <si>
+    <t>properties</t>
+  </si>
+  <si>
+    <t>vehicles</t>
+  </si>
+  <si>
+    <t>deductions</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>credit</t>
@@ -683,6 +704,9 @@
   </si>
   <si>
     <t>result</t>
+  </si>
+  <si>
+    <t>state_tax_results</t>
   </si>
   <si>
     <t>## ENTITIES (name | number: 1 or *)</t>
@@ -4056,7 +4080,9 @@
       <c r="C226" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D226" s="2"/>
+      <c r="D226" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
@@ -4068,7 +4094,9 @@
       <c r="C227" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D227" s="2"/>
+      <c r="D227" s="2" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
@@ -4080,7 +4108,9 @@
       <c r="C228" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D228" s="2"/>
+      <c r="D228" s="2" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
@@ -4092,7 +4122,9 @@
       <c r="C229" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D229" s="2"/>
+      <c r="D229" s="2" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
@@ -4104,7 +4136,9 @@
       <c r="C230" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D230" s="2"/>
+      <c r="D230" s="2" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
@@ -4116,7 +4150,9 @@
       <c r="C231" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D231" s="2"/>
+      <c r="D231" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
@@ -4128,7 +4164,9 @@
       <c r="C232" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D232" s="2"/>
+      <c r="D232" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
@@ -4140,7 +4178,9 @@
       <c r="C233" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D233" s="2"/>
+      <c r="D233" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
@@ -4152,7 +4192,9 @@
       <c r="C234" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D234" s="2"/>
+      <c r="D234" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
@@ -4164,7 +4206,9 @@
       <c r="C235" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D235" s="2"/>
+      <c r="D235" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
@@ -4176,7 +4220,9 @@
       <c r="C236" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D236" s="2"/>
+      <c r="D236" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
@@ -4188,7 +4234,9 @@
       <c r="C237" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D237" s="2"/>
+      <c r="D237" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
@@ -4200,43 +4248,51 @@
       <c r="C238" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D238" s="2"/>
+      <c r="D238" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D239" s="2"/>
+      <c r="D239" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D240" s="2"/>
+      <c r="D240" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D241" s="2"/>
+      <c r="D241" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
@@ -4248,11 +4304,13 @@
       <c r="C242" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D242" s="2"/>
+      <c r="D242" s="2" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B243" s="6"/>
       <c r="C243" s="6"/>
@@ -4260,10 +4318,10 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="2"/>
@@ -4273,17 +4331,17 @@
         <v>7</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
@@ -4293,7 +4351,7 @@
         <v>32</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
@@ -4303,7 +4361,7 @@
         <v>76</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
@@ -4313,7 +4371,7 @@
         <v>93</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
@@ -4323,7 +4381,7 @@
         <v>104</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
@@ -4333,7 +4391,7 @@
         <v>122</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
@@ -4343,7 +4401,7 @@
         <v>130</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
@@ -4353,7 +4411,7 @@
         <v>134</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
@@ -4363,7 +4421,7 @@
         <v>153</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
@@ -4373,7 +4431,7 @@
         <v>157</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
@@ -4383,7 +4441,7 @@
         <v>166</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
@@ -4393,7 +4451,7 @@
         <v>173</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
@@ -4403,7 +4461,7 @@
         <v>187</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
@@ -4413,17 +4471,17 @@
         <v>196</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
@@ -4433,14 +4491,14 @@
         <v>207</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B262" s="6"/>
       <c r="C262" s="6"/>
@@ -4448,20 +4506,20 @@
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
@@ -4471,7 +4529,7 @@
         <v>7</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>

--- a/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
+++ b/sampleprojects/TaxReturn/excel/TaxReturn_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
   <si>
     <t>MAP: TaxReturn</t>
   </si>
@@ -673,6 +673,27 @@
     <t># Multiple instance entities</t>
   </si>
   <si>
+    <t>state_period</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>end_date</t>
+  </si>
+  <si>
+    <t>resident_status</t>
+  </si>
+  <si>
+    <t>days_in_state</t>
+  </si>
+  <si>
+    <t>expected_reciprocity_state</t>
+  </si>
+  <si>
+    <t>expected_nonresident_source_income</t>
+  </si>
+  <si>
     <t>## CREATE ENTITIES (entity | tag | id | list)</t>
   </si>
   <si>
@@ -707,6 +728,9 @@
   </si>
   <si>
     <t>state_tax_results</t>
+  </si>
+  <si>
+    <t>state_periods</t>
   </si>
   <si>
     <t>## ENTITIES (name | number: 1 or *)</t>
@@ -4063,476 +4087,626 @@
       <c r="D224" s="6"/>
     </row>
     <row r="225">
-      <c r="A225" s="6" t="s">
+      <c r="A225" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C225" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B225" s="6"/>
-      <c r="C225" s="6"/>
-      <c r="D225" s="6"/>
+      <c r="D225" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>32</v>
+        <v>206</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>32</v>
+        <v>206</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>6</v>
+        <v>219</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>220</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>6</v>
+        <v>219</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>221</v>
+        <v>36</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>6</v>
+        <v>219</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>222</v>
+        <v>36</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>104</v>
+        <v>222</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>104</v>
+        <v>222</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>6</v>
+        <v>219</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>223</v>
+        <v>11</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>122</v>
+        <v>223</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>122</v>
+        <v>223</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>6</v>
+        <v>219</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>224</v>
+        <v>8</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>225</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>134</v>
+        <v>224</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>134</v>
+        <v>224</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>226</v>
+        <v>11</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>153</v>
+        <v>225</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>153</v>
+        <v>225</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D233" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>226</v>
-      </c>
+      <c r="B234" s="6"/>
+      <c r="C234" s="6"/>
+      <c r="D234" s="6"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
-        <v>187</v>
+        <v>93</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>187</v>
+        <v>93</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>227</v>
+        <v>122</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>227</v>
+        <v>122</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B243" s="6"/>
-      <c r="C243" s="6"/>
-      <c r="D243" s="6"/>
+      <c r="A243" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>229</v>
+        <v>187</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>32</v>
+        <v>196</v>
       </c>
       <c r="B247" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D247" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>76</v>
+        <v>234</v>
       </c>
       <c r="B248" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="B249" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D249" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="B250" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D250" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C251" s="2"/>
-      <c r="D251" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>130</v>
+        <v>219</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C252" s="2"/>
-      <c r="D252" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C253" s="2"/>
-      <c r="D253" s="2"/>
+      <c r="A253" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B253" s="6"/>
+      <c r="C253" s="6"/>
+      <c r="D253" s="6"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>153</v>
+        <v>235</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>227</v>
+        <v>104</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>207</v>
+        <v>122</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
-      <c r="A262" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="B262" s="6"/>
-      <c r="C262" s="6"/>
-      <c r="D262" s="6"/>
+      <c r="A262" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C271" s="2"/>
+      <c r="D271" s="2"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B273" s="6"/>
+      <c r="C273" s="6"/>
+      <c r="D273" s="6"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C275" s="2"/>
+      <c r="D275" s="2"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
